--- a/tables/tables performance/all_Disc_Cum_Gain.xlsx
+++ b/tables/tables performance/all_Disc_Cum_Gain.xlsx
@@ -682,52 +682,52 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.528851431563885</v>
+        <v>8.835979671752929</v>
       </c>
       <c r="C5" t="n">
-        <v>5.476269131679469</v>
+        <v>9.559724232824683</v>
       </c>
       <c r="D5" t="n">
-        <v>5.129382964472142</v>
+        <v>8.462654460139133</v>
       </c>
       <c r="E5" t="n">
-        <v>4.760023068463258</v>
+        <v>9.191245476676407</v>
       </c>
       <c r="F5" t="n">
-        <v>5.351322288218326</v>
+        <v>8.563762256151277</v>
       </c>
       <c r="G5" t="n">
-        <v>5.551812382250715</v>
+        <v>9.290149251731492</v>
       </c>
       <c r="H5" t="n">
-        <v>5.410515639162346</v>
+        <v>7.635471311338192</v>
       </c>
       <c r="I5" t="n">
-        <v>5.65366027255273</v>
+        <v>9.43732295944536</v>
       </c>
       <c r="J5" t="n">
-        <v>4.651234617851287</v>
+        <v>7.184542101464745</v>
       </c>
       <c r="K5" t="n">
-        <v>5.571304974753935</v>
+        <v>9.273174641548325</v>
       </c>
       <c r="L5" t="n">
-        <v>5.440062922849481</v>
+        <v>8.228898482075106</v>
       </c>
       <c r="M5" t="n">
-        <v>5.743478618297891</v>
+        <v>9.238389555606799</v>
       </c>
       <c r="N5" t="n">
-        <v>5.119593883260483</v>
+        <v>8.642965732817014</v>
       </c>
       <c r="O5" t="n">
-        <v>4.972791057203125</v>
+        <v>8.067012629927646</v>
       </c>
       <c r="P5" t="n">
-        <v>5.030885380273817</v>
+        <v>8.755237688865707</v>
       </c>
       <c r="Q5" t="n">
-        <v>4.509344649467621</v>
+        <v>8.238425597662363</v>
       </c>
     </row>
     <row r="6">
@@ -843,221 +843,221 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>synth_credit_card_fraud_label_Disc_Cum_Gain.csv</t>
+          <t>kdd_Disc_Cum_Gain.csv</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>7.719134892317284</v>
+        <v>2.132322127495722</v>
       </c>
       <c r="C8" t="n">
-        <v>8.033668907953416</v>
+        <v>1.698183451959689</v>
       </c>
       <c r="D8" t="n">
-        <v>7.599867423193221</v>
+        <v>2.103662313592446</v>
       </c>
       <c r="E8" t="n">
-        <v>7.627751682274158</v>
+        <v>1.983977864965875</v>
       </c>
       <c r="F8" t="n">
-        <v>7.590330629100767</v>
+        <v>2.196553760012084</v>
       </c>
       <c r="G8" t="n">
-        <v>8.103701475043229</v>
+        <v>1.949255877632042</v>
       </c>
       <c r="H8" t="n">
-        <v>7.466874274406821</v>
+        <v>2.042231825347975</v>
       </c>
       <c r="I8" t="n">
-        <v>7.967823301764834</v>
+        <v>1.96672220549526</v>
       </c>
       <c r="J8" t="n">
-        <v>7.344604027564234</v>
+        <v>2.259671252463235</v>
       </c>
       <c r="K8" t="n">
-        <v>8.101138861619729</v>
+        <v>2.217607837160494</v>
       </c>
       <c r="L8" t="n">
-        <v>7.64758701308404</v>
+        <v>2.159304140862965</v>
       </c>
       <c r="M8" t="n">
-        <v>7.951855938636146</v>
+        <v>2.301150060341916</v>
       </c>
       <c r="N8" t="n">
-        <v>7.727350816705478</v>
+        <v>2.110111252320768</v>
       </c>
       <c r="O8" t="n">
-        <v>7.841144254382921</v>
+        <v>1.993520912244653</v>
       </c>
       <c r="P8" t="n">
-        <v>7.464258705321411</v>
+        <v>2.040604806454875</v>
       </c>
       <c r="Q8" t="n">
-        <v>7.748395877221177</v>
+        <v>1.937275131220662</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>synth_mobile_money_fraud_label_Disc_Cum_Gain.csv</t>
+          <t>synth_credit_card_fraud_label_Disc_Cum_Gain.csv</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4.167058192581836</v>
+        <v>7.719134892317284</v>
       </c>
       <c r="C9" t="n">
-        <v>6.70541126135025</v>
+        <v>8.033668907953416</v>
       </c>
       <c r="D9" t="n">
-        <v>5.282494996588329</v>
+        <v>7.599867423193221</v>
       </c>
       <c r="E9" t="n">
-        <v>6.519052912759044</v>
+        <v>7.627751682274158</v>
       </c>
       <c r="F9" t="n">
-        <v>3.712985043218139</v>
+        <v>7.590330629100767</v>
       </c>
       <c r="G9" t="n">
-        <v>6.719596340063527</v>
+        <v>8.103701475043229</v>
       </c>
       <c r="H9" t="n">
-        <v>2.777456426777341</v>
+        <v>7.466874274406821</v>
       </c>
       <c r="I9" t="n">
-        <v>6.793519010436402</v>
+        <v>7.967823301764834</v>
       </c>
       <c r="J9" t="n">
-        <v>3.346072835132588</v>
+        <v>7.344604027564234</v>
       </c>
       <c r="K9" t="n">
-        <v>6.669926974332904</v>
+        <v>8.101138861619729</v>
       </c>
       <c r="L9" t="n">
-        <v>4.481481241325641</v>
+        <v>7.64758701308404</v>
       </c>
       <c r="M9" t="n">
-        <v>6.655695815231726</v>
+        <v>7.951855938636146</v>
       </c>
       <c r="N9" t="n">
-        <v>5.146989860002743</v>
+        <v>7.727350816705478</v>
       </c>
       <c r="O9" t="n">
-        <v>6.588749158647445</v>
+        <v>7.841144254382921</v>
       </c>
       <c r="P9" t="n">
-        <v>5.174383528576941</v>
+        <v>7.464258705321411</v>
       </c>
       <c r="Q9" t="n">
-        <v>6.655575067313579</v>
+        <v>7.748395877221177</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>telco_customer_churn_Disc_Cum_Gain.csv</t>
+          <t>synth_mobile_money_fraud_label_Disc_Cum_Gain.csv</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.945310818632594</v>
+        <v>4.167058192581836</v>
       </c>
       <c r="C10" t="n">
-        <v>5.359408774323904</v>
+        <v>6.70541126135025</v>
       </c>
       <c r="D10" t="n">
-        <v>5.293313974978733</v>
+        <v>5.282494996588329</v>
       </c>
       <c r="E10" t="n">
-        <v>4.005426115820653</v>
+        <v>6.519052912759044</v>
       </c>
       <c r="F10" t="n">
-        <v>3.269934567615549</v>
+        <v>3.712985043218139</v>
       </c>
       <c r="G10" t="n">
-        <v>5.343623846657927</v>
+        <v>6.719596340063527</v>
       </c>
       <c r="H10" t="n">
-        <v>4.037020043304304</v>
+        <v>2.777456426777341</v>
       </c>
       <c r="I10" t="n">
-        <v>5.669253411635927</v>
+        <v>6.793519010436402</v>
       </c>
       <c r="J10" t="n">
-        <v>3.553208167021318</v>
+        <v>3.346072835132588</v>
       </c>
       <c r="K10" t="n">
-        <v>5.983358938825585</v>
+        <v>6.669926974332904</v>
       </c>
       <c r="L10" t="n">
-        <v>5.292401782257718</v>
+        <v>4.481481241325641</v>
       </c>
       <c r="M10" t="n">
-        <v>4.268999587824694</v>
+        <v>6.655695815231726</v>
       </c>
       <c r="N10" t="n">
-        <v>5.327228263551255</v>
+        <v>5.146989860002743</v>
       </c>
       <c r="O10" t="n">
-        <v>3.83606615918493</v>
+        <v>6.588749158647445</v>
       </c>
       <c r="P10" t="n">
-        <v>4.890031022253885</v>
+        <v>5.174383528576941</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.828077568766288</v>
+        <v>6.655575067313579</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>ulb_credit_card_fraud_label_Disc_Cum_Gain.csv</t>
+          <t>telco_customer_churn_Disc_Cum_Gain.csv</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>21.72531735311019</v>
+        <v>3.945310818632594</v>
       </c>
       <c r="C11" t="n">
-        <v>22.03950570117104</v>
+        <v>5.359408774323904</v>
       </c>
       <c r="D11" t="n">
-        <v>21.85400274370572</v>
+        <v>5.293313974978733</v>
       </c>
       <c r="E11" t="n">
-        <v>22.03829279568363</v>
+        <v>4.005426115820653</v>
       </c>
       <c r="F11" t="n">
-        <v>21.86351085655177</v>
+        <v>3.269934567615549</v>
       </c>
       <c r="G11" t="n">
-        <v>22.00901106265895</v>
+        <v>5.343623846657927</v>
       </c>
       <c r="H11" t="n">
-        <v>21.67280487518566</v>
+        <v>4.037020043304304</v>
       </c>
       <c r="I11" t="n">
-        <v>21.95474051382001</v>
+        <v>5.669253411635927</v>
       </c>
       <c r="J11" t="n">
-        <v>21.56488123702485</v>
+        <v>3.553208167021318</v>
       </c>
       <c r="K11" t="n">
-        <v>22.00019145227312</v>
+        <v>5.983358938825585</v>
       </c>
       <c r="L11" t="n">
-        <v>21.76824490794295</v>
+        <v>5.292401782257718</v>
       </c>
       <c r="M11" t="n">
-        <v>22.07051524222696</v>
+        <v>4.268999587824694</v>
       </c>
       <c r="N11" t="n">
-        <v>21.81069717886417</v>
+        <v>5.327228263551255</v>
       </c>
       <c r="O11" t="n">
-        <v>22.02633506489451</v>
+        <v>3.83606615918493</v>
       </c>
       <c r="P11" t="n">
-        <v>21.80454971066668</v>
+        <v>4.890031022253885</v>
       </c>
       <c r="Q11" t="n">
-        <v>22.09679816599244</v>
+        <v>3.828077568766288</v>
       </c>
     </row>
     <row r="12">
